--- a/Portabox-SEO-Build-Sheet (updated).xlsx
+++ b/Portabox-SEO-Build-Sheet (updated).xlsx
@@ -3003,7 +3003,8 @@
     <col customWidth="1" min="13" max="13" width="78.0"/>
     <col customWidth="1" min="14" max="14" width="62.0"/>
     <col customWidth="1" min="15" max="15" width="14.0"/>
-    <col customWidth="1" min="16" max="26" width="8.71"/>
+    <col customWidth="1" min="16" max="16" width="86.0"/>
+    <col customWidth="1" min="17" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
@@ -3056,6 +3057,11 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
@@ -3094,6 +3100,11 @@
       <c r="O2" t="inlineStr">
         <is>
           <t>Not a page</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Not a page on this site. These are Google listings and the SEO team said to leave them for now.</t>
         </is>
       </c>
     </row>
@@ -3134,6 +3145,11 @@
           <t>Not a page</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Not a page on this site. These are Google listings and the SEO team said to leave them for now.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
@@ -3172,6 +3188,11 @@
           <t>Not a page</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Not a page on this site. These are Google listings and the SEO team said to leave them for now.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
@@ -3208,6 +3229,11 @@
       <c r="O5" t="inlineStr">
         <is>
           <t>Not a page</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Not a page on this site. These are Google listings and the SEO team said to leave them for now.</t>
         </is>
       </c>
     </row>
@@ -3488,6 +3514,11 @@
           <t>Not a page</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>BUILT, but not as a page: the schema is generated into the head of all 105 pages — Organization everywhere, SelfStorage on each region hub and facility, FAQPage and BreadcrumbList where they apply.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="s">
@@ -3872,7 +3903,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3950,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3997,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4044,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4091,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4138,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4185,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4232,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4279,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4326,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4373,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4420,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4467,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4486,6 +4517,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>BLOCKED, needs one decision: this suburb name exists in more than one state, so the page would land under the wrong region hub. Confirm the state and it is a few minutes to build.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="19" t="s">
@@ -4533,6 +4569,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>BLOCKED, needs one decision: this suburb name exists in more than one state, so the page would land under the wrong region hub. Confirm the state and it is a few minutes to build.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="19" t="s">
@@ -4577,7 +4618,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4665,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4712,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4759,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4806,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4853,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4862,6 +4903,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>BLOCKED, needs one decision: this suburb name exists in more than one state, so the page would land under the wrong region hub. Confirm the state and it is a few minutes to build.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="19" t="s">
@@ -4906,7 +4952,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4999,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5003,6 +5049,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>BLOCKED, needs one decision: this suburb name exists in more than one state, so the page would land under the wrong region hub. Confirm the state and it is a few minutes to build.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="19" t="s">
@@ -5047,7 +5098,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5145,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5192,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5239,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5286,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5333,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5380,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5427,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5423,7 +5474,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5521,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5568,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5615,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5662,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5709,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5756,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5803,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5799,7 +5850,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5897,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5887,7 +5938,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5979,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -5969,7 +6020,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6010,7 +6061,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6100,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6180,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6219,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6258,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6297,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6336,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6324,7 +6375,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6414,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6453,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6492,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6531,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6570,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6609,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6648,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6687,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6675,7 +6726,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6765,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6804,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6843,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6831,7 +6882,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6921,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6913,7 +6964,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6954,7 +7005,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -6995,7 +7046,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7087,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7126,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7163,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7200,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7239,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7278,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7319,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -7314,6 +7365,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="23" t="s">
@@ -7357,6 +7413,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="23" t="s">
@@ -7400,6 +7461,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="23" t="s">
@@ -7443,6 +7509,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="23" t="s">
@@ -7486,6 +7557,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="23" t="s">
@@ -7529,6 +7605,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="23" t="s">
@@ -7572,6 +7653,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="23" t="s">
@@ -7615,6 +7701,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="23" t="s">
@@ -7658,6 +7749,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="23" t="s">
@@ -7701,6 +7797,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="23" t="s">
@@ -7744,6 +7845,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="23" t="s">
@@ -7787,6 +7893,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="23" t="s">
@@ -7830,6 +7941,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="23" t="s">
@@ -7873,6 +7989,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="23" t="s">
@@ -7916,6 +8037,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="23" t="s">
@@ -7959,6 +8085,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="23" t="s">
@@ -8002,6 +8133,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="23" t="s">
@@ -8045,6 +8181,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="23" t="s">
@@ -8088,6 +8229,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="23" t="s">
@@ -8131,6 +8277,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="23" t="s">
@@ -8174,6 +8325,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="23" t="s">
@@ -8217,6 +8373,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="23" t="s">
@@ -8260,6 +8421,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="23" t="s">
@@ -8303,6 +8469,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="23" t="s">
@@ -8346,6 +8517,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="23" t="s">
@@ -8389,6 +8565,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="23" t="s">
@@ -8432,6 +8613,11 @@
           <t>Not built yet</t>
         </is>
       </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="23" t="s">
@@ -8473,6 +8659,11 @@
       <c r="O127" t="inlineStr">
         <is>
           <t>Not built yet</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
         </is>
       </c>
     </row>

--- a/Portabox-SEO-Build-Sheet (updated).xlsx
+++ b/Portabox-SEO-Build-Sheet (updated).xlsx
@@ -3516,7 +3516,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>BUILT, but not as a page: the schema is generated into the head of all 105 pages — Organization everywhere, SelfStorage on each region hub and facility, FAQPage and BreadcrumbList where they apply.</t>
+          <t>BUILT, but not as a page: the schema is generated into the head of all 127 pages — Organization everywhere, SelfStorage on each region hub and facility, FAQPage and BreadcrumbList where they apply.</t>
         </is>
       </c>
     </row>
@@ -7362,12 +7362,12 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — merged into its region hub. The hub already covers this ground, so the old URL 301s to /self-storage/melbourne/ rather than running a second page against it.</t>
         </is>
       </c>
     </row>
@@ -7410,12 +7410,12 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/mornington/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Mornington, Melbourne, Victoria, 3931, Australia — 61 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7458,12 +7458,12 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/penrith/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Penrith, Sydney, New South Wales, 2750, Australia — 25 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/gold-coast/burleigh/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Burleigh Heads, Gold Coast, Queensland, Australia — 56 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/port-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Port Melbourne, Melbourne, Victoria, 3207, Australia — 13 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7607,7 +7607,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>BLOCKED, needs one decision: this name is a real suburb in more than one of our cities, so geocoding cannot pick the hub for us. Candidates, each in depot range: Brisbane (37 km, Queensland); Sydney (137 km, New South Wales); Melbourne (71 km, Victoria). Say which one and the page is a few minutes to build.</t>
         </is>
       </c>
     </row>
@@ -7650,12 +7650,12 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/south-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: South Melbourne, Melbourne, Victoria, 3205, Australia — 18 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/tullamarine/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Tullamarine, Melbourne, Victoria, 3043, Australia — 19 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7746,12 +7746,12 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/moorabbin/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Moorabbin, Melbourne, Victoria, 3189, Australia — 33 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/yatala/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Yatala, Logan City, Queensland, 4207, Australia — 8 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -7842,12 +7842,12 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/capalaba/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Capalaba, Logan City, Brisbane, Redland City, Queensland, Australia — 32 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -7890,12 +7890,12 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/north-sydney/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: North Sydney, New South Wales, 2060, Australia — 37 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — dropped as a service page. Fremantle is in WA and the nearest depot is Adelaide, well past the 200 km standard-delivery range, so a page promising service there would not be true. The old URL 301s to /locations/regional-australia/, which is where a WA enquiry should land.</t>
         </is>
       </c>
     </row>
@@ -7986,12 +7986,12 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/brookvale/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Brookvale, Northern Beaches, Sydney, New South Wales, Australia — 43 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/marrickville/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Marrickville, Inner West, Sydney, New South Wales, 2204, Australia — 36 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8082,12 +8082,12 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — merged, not rebuilt. "Eastern Suburbs" is a region, not a suburb, so there is nothing to geocode and no single page it maps to. The old URL 301s to /self-storage/sydney/, which lists every Sydney suburb page beneath it, Bondi Junction among them.</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>BLOCKED, needs one decision: this name is a real suburb in more than one of our cities, so geocoding cannot pick the hub for us. Candidates, each in depot range: Sydney (42 km, New South Wales); Melbourne (15 km, Victoria); Adelaide (30 km, South Australia). Say which one and the page is a few minutes to build.</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/wollongong/unanderra/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Unanderra, Wollongong, New South Wales, Australia — 97 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/north-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: North Melbourne, Melbourne, Victoria, 3051, Australia — 16 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -8274,12 +8274,12 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/chermside/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Chermside, Brisbane, Queensland, 4032, Australia — 58 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -8322,12 +8322,12 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/gladesville/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Gladesville, Sydney, New South Wales, 2111, Australia — 27 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8370,12 +8370,12 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/altona/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Altona, Melbourne, Victoria, 3018, Australia — 5 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/gold-coast/ormeau/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Ormeau, Queensland, Australia — 8 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/aspley/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Aspley, Brisbane, Queensland, Australia — 62 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -8514,12 +8514,12 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/brendale/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Brendale, Brisbane, Queensland, Australia — 70 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>BLOCKED, needs one decision: this name is a real suburb in more than one of our cities, so geocoding cannot pick the hub for us. Candidates, each in depot range: Melbourne (25 km, Victoria); Adelaide (38 km, South Australia). Say which one and the page is a few minutes to build.</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/rozelle/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Rozelle, Inner West, Sydney, New South Wales, 2039, Australia — 34 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8658,12 +8658,12 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Not built yet</t>
+          <t>Live (301)</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>NOT A BUILD: the sheet says decide merge or rebuild per page and do not migrate as-is. Each of these needs a call on whether it folds into its region hub or gets rebuilt — that is your decision, not a page to generate.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/balmain/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Balmain, Inner West, Sydney, New South Wales, 2041, Australia — 34 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>

--- a/Portabox-SEO-Build-Sheet (updated).xlsx
+++ b/Portabox-SEO-Build-Sheet (updated).xlsx
@@ -7362,12 +7362,12 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>DONE — merged into its region hub. The hub already covers this ground, so the old URL 301s to /self-storage/melbourne/ rather than running a second page against it.</t>
+          <t>DONE — merged into its region hub. The hub already covers this ground, so the old URL permanently redirects to /self-storage/melbourne/ rather than running a second page against it.</t>
         </is>
       </c>
     </row>
@@ -7410,12 +7410,12 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/mornington/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Mornington, Melbourne, Victoria, 3931, Australia — 61 km by road from the Melbourne depot at Laverton North.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/melbourne/mornington/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Mornington, Melbourne, Victoria, 3931, Australia — 61 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7458,12 +7458,12 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/penrith/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Penrith, Sydney, New South Wales, 2750, Australia — 25 km by road from the Sydney depot at Blacktown.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/sydney/penrith/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Penrith, Sydney, New South Wales, 2750, Australia — 25 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/gold-coast/burleigh/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Burleigh Heads, Gold Coast, Queensland, Australia — 56 km by road from the Brisbane depot at Gilberton.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/gold-coast/burleigh/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Burleigh Heads, Gold Coast, Queensland, Australia — 56 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/port-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Port Melbourne, Melbourne, Victoria, 3207, Australia — 13 km by road from the Melbourne depot at Laverton North.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/melbourne/port-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Port Melbourne, Melbourne, Victoria, 3207, Australia — 13 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7650,12 +7650,12 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/south-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: South Melbourne, Melbourne, Victoria, 3205, Australia — 18 km by road from the Melbourne depot at Laverton North.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/melbourne/south-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: South Melbourne, Melbourne, Victoria, 3205, Australia — 18 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/tullamarine/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Tullamarine, Melbourne, Victoria, 3043, Australia — 19 km by road from the Melbourne depot at Laverton North.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/melbourne/tullamarine/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Tullamarine, Melbourne, Victoria, 3043, Australia — 19 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7746,12 +7746,12 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/moorabbin/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Moorabbin, Melbourne, Victoria, 3189, Australia — 33 km by road from the Melbourne depot at Laverton North.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/melbourne/moorabbin/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Moorabbin, Melbourne, Victoria, 3189, Australia — 33 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/yatala/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Yatala, Logan City, Queensland, 4207, Australia — 8 km by road from the Brisbane depot at Gilberton.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/brisbane/yatala/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Yatala, Logan City, Queensland, 4207, Australia — 8 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -7842,12 +7842,12 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/capalaba/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Capalaba, Logan City, Brisbane, Redland City, Queensland, Australia — 32 km by road from the Brisbane depot at Gilberton.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/brisbane/capalaba/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Capalaba, Logan City, Brisbane, Redland City, Queensland, Australia — 32 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -7890,12 +7890,12 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/north-sydney/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: North Sydney, New South Wales, 2060, Australia — 37 km by road from the Sydney depot at Blacktown.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/sydney/north-sydney/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: North Sydney, New South Wales, 2060, Australia — 37 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>DONE — dropped as a service page. Fremantle is in WA and the nearest depot is Adelaide, well past the 200 km standard-delivery range, so a page promising service there would not be true. The old URL 301s to /locations/regional-australia/, which is where a WA enquiry should land.</t>
+          <t>DONE — dropped as a service page. Fremantle is in WA and the nearest depot is Adelaide, well past the 200 km standard-delivery range, so a page promising service there would not be true. The old URL permanently redirects to /locations/regional-australia/, which is where a WA enquiry should land.</t>
         </is>
       </c>
     </row>
@@ -7986,12 +7986,12 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/brookvale/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Brookvale, Northern Beaches, Sydney, New South Wales, Australia — 43 km by road from the Sydney depot at Blacktown.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/sydney/brookvale/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Brookvale, Northern Beaches, Sydney, New South Wales, Australia — 43 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/marrickville/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Marrickville, Inner West, Sydney, New South Wales, 2204, Australia — 36 km by road from the Sydney depot at Blacktown.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/sydney/marrickville/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Marrickville, Inner West, Sydney, New South Wales, 2204, Australia — 36 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8082,12 +8082,12 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>DONE — merged, not rebuilt. "Eastern Suburbs" is a region, not a suburb, so there is nothing to geocode and no single page it maps to. The old URL 301s to /self-storage/sydney/, which lists every Sydney suburb page beneath it, Bondi Junction among them.</t>
+          <t>DONE — merged, not rebuilt. "Eastern Suburbs" is a region, not a suburb, so there is nothing to geocode and no single page it maps to. The old URL permanently redirects to /self-storage/sydney/, which lists every Sydney suburb page beneath it, Bondi Junction among them.</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/wollongong/unanderra/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Unanderra, Wollongong, New South Wales, Australia — 97 km by road from the Sydney depot at Blacktown.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/wollongong/unanderra/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Unanderra, Wollongong, New South Wales, Australia — 97 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/north-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: North Melbourne, Melbourne, Victoria, 3051, Australia — 16 km by road from the Melbourne depot at Laverton North.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/melbourne/north-melbourne/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: North Melbourne, Melbourne, Victoria, 3051, Australia — 16 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -8274,12 +8274,12 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/chermside/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Chermside, Brisbane, Queensland, 4032, Australia — 58 km by road from the Brisbane depot at Gilberton.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/brisbane/chermside/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Chermside, Brisbane, Queensland, 4032, Australia — 58 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -8322,12 +8322,12 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/gladesville/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Gladesville, Sydney, New South Wales, 2111, Australia — 27 km by road from the Sydney depot at Blacktown.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/sydney/gladesville/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Gladesville, Sydney, New South Wales, 2111, Australia — 27 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8370,12 +8370,12 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/melbourne/altona/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Altona, Melbourne, Victoria, 3018, Australia — 5 km by road from the Melbourne depot at Laverton North.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/melbourne/altona/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Altona, Melbourne, Victoria, 3018, Australia — 5 km by road from the Melbourne depot at Laverton North.</t>
         </is>
       </c>
     </row>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/gold-coast/ormeau/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Ormeau, Queensland, Australia — 8 km by road from the Brisbane depot at Gilberton.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/gold-coast/ormeau/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Ormeau, Queensland, Australia — 8 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/aspley/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Aspley, Brisbane, Queensland, Australia — 62 km by road from the Brisbane depot at Gilberton.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/brisbane/aspley/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Aspley, Brisbane, Queensland, Australia — 62 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -8514,12 +8514,12 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/brisbane/brendale/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Brendale, Brisbane, Queensland, Australia — 70 km by road from the Brisbane depot at Gilberton.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/brisbane/brendale/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Brendale, Brisbane, Queensland, Australia — 70 km by road from the Brisbane depot at Gilberton.</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/rozelle/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Rozelle, Inner West, Sydney, New South Wales, 2039, Australia — 34 km by road from the Sydney depot at Blacktown.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/sydney/rozelle/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Rozelle, Inner West, Sydney, New South Wales, 2039, Australia — 34 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
@@ -8658,12 +8658,12 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Live (301)</t>
+          <t>Live (308 redirect)</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>DONE — rebuilt, not migrated as-is. The old URL 301s to /self-storage/sydney/balmain/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Balmain, Inner West, Sydney, New South Wales, 2041, Australia — 34 km by road from the Sydney depot at Blacktown.</t>
+          <t>DONE — rebuilt, not migrated as-is. The old URL permanently redirects to /self-storage/sydney/balmain/, a suburb page written from scratch. Which hub it belongs under was settled by geocoding the name: Balmain, Inner West, Sydney, New South Wales, 2041, Australia — 34 km by road from the Sydney depot at Blacktown.</t>
         </is>
       </c>
     </row>
